--- a/BoM.xlsx
+++ b/BoM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://graceindustriesllc-my.sharepoint.com/personal/bmcnerney_hauglandllc_com/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bedga\PycharmProjects\Project-MJOLNIR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="127" documentId="8_{A6A8C95E-9056-4A5C-9A2A-849EE096CD16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7E2122DE-E03C-4E79-884B-91F122C599D4}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A1ACCAC-3E31-46AF-80AA-57242DD3B05B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28890" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{BE61A943-5BBA-42A8-A103-D5A6C0FF29A3}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11295" xr2:uid="{BE61A943-5BBA-42A8-A103-D5A6C0FF29A3}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
   <si>
     <t>Description</t>
   </si>
@@ -129,6 +129,12 @@
   </si>
   <si>
     <t>Tacticle Gloves</t>
+  </si>
+  <si>
+    <t>Raspberry Pi 3b</t>
+  </si>
+  <si>
+    <t>R Pi</t>
   </si>
 </sst>
 </file>
@@ -270,10 +276,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -594,22 +596,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BFD61B24-C7D2-4C0E-89FA-F5F9ED5B437B}">
   <dimension ref="C4:J36"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.7265625" style="1"/>
-    <col min="2" max="2" width="8.7265625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="11.26953125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="22.7265625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="39.81640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="27.08984375" style="1" customWidth="1"/>
-    <col min="7" max="7" width="6.54296875" style="1" customWidth="1"/>
-    <col min="8" max="8" width="12.26953125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.08984375" style="1" customWidth="1"/>
-    <col min="10" max="10" width="10.26953125" style="1" customWidth="1"/>
-    <col min="11" max="16384" width="8.7265625" style="1"/>
+    <col min="1" max="1" width="8.7109375" style="1"/>
+    <col min="2" max="2" width="8.7109375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="11.28515625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="22.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="39.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="27.140625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="6.5703125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="12.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.140625" style="1" customWidth="1"/>
+    <col min="10" max="10" width="10.28515625" style="1" customWidth="1"/>
+    <col min="11" max="16384" width="8.7109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="3:10" x14ac:dyDescent="0.35">
+    <row r="4" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C4" s="2" t="s">
         <v>5</v>
       </c>
@@ -635,7 +637,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="3:10" x14ac:dyDescent="0.35">
+    <row r="5" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C5" s="3"/>
       <c r="D5" s="3" t="s">
         <v>8</v>
@@ -658,7 +660,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="3:10" x14ac:dyDescent="0.35">
+    <row r="6" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C6" s="4"/>
       <c r="D6" s="4" t="s">
         <v>10</v>
@@ -683,7 +685,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="7" spans="3:10" x14ac:dyDescent="0.35">
+    <row r="7" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C7" s="3"/>
       <c r="D7" s="3" t="s">
         <v>15</v>
@@ -703,7 +705,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="3:10" x14ac:dyDescent="0.35">
+    <row r="8" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C8" s="4"/>
       <c r="D8" s="4" t="s">
         <v>16</v>
@@ -720,7 +722,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="3:10" x14ac:dyDescent="0.35">
+    <row r="9" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C9" s="3"/>
       <c r="D9" s="3" t="s">
         <v>19</v>
@@ -737,7 +739,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="3:10" x14ac:dyDescent="0.35">
+    <row r="10" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C10" s="4"/>
       <c r="D10" s="4" t="s">
         <v>20</v>
@@ -754,7 +756,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="3:10" x14ac:dyDescent="0.35">
+    <row r="11" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C11" s="3"/>
       <c r="D11" s="3" t="s">
         <v>21</v>
@@ -771,7 +773,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="3:10" x14ac:dyDescent="0.35">
+    <row r="12" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C12" s="4"/>
       <c r="D12" s="4" t="s">
         <v>25</v>
@@ -795,7 +797,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="3:10" x14ac:dyDescent="0.35">
+    <row r="13" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C13" s="3"/>
       <c r="D13" s="3" t="s">
         <v>29</v>
@@ -815,20 +817,28 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="3:10" x14ac:dyDescent="0.35">
+    <row r="14" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C14" s="4"/>
-      <c r="D14" s="4"/>
+      <c r="D14" s="4" t="s">
+        <v>30</v>
+      </c>
       <c r="E14" s="4"/>
       <c r="F14" s="4"/>
-      <c r="G14" s="4"/>
-      <c r="H14" s="4"/>
-      <c r="I14" s="7"/>
+      <c r="G14" s="4">
+        <v>1</v>
+      </c>
+      <c r="H14" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="I14" s="7">
+        <v>0</v>
+      </c>
       <c r="J14" s="7">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="3:10" x14ac:dyDescent="0.35">
+    <row r="15" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C15" s="3"/>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
@@ -841,7 +851,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="3:10" x14ac:dyDescent="0.35">
+    <row r="16" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C16" s="4"/>
       <c r="D16" s="4"/>
       <c r="E16" s="4"/>
@@ -854,7 +864,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="3:10" x14ac:dyDescent="0.35">
+    <row r="17" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C17" s="3"/>
       <c r="D17" s="3"/>
       <c r="E17" s="3"/>
@@ -867,7 +877,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="3:10" x14ac:dyDescent="0.35">
+    <row r="18" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C18" s="4"/>
       <c r="D18" s="4"/>
       <c r="E18" s="4"/>
@@ -880,7 +890,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="3:10" x14ac:dyDescent="0.35">
+    <row r="19" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C19" s="3"/>
       <c r="D19" s="3"/>
       <c r="E19" s="3"/>
@@ -893,7 +903,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="3:10" x14ac:dyDescent="0.35">
+    <row r="20" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C20" s="4"/>
       <c r="D20" s="4"/>
       <c r="E20" s="4"/>
@@ -906,7 +916,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="3:10" x14ac:dyDescent="0.35">
+    <row r="21" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C21" s="3"/>
       <c r="D21" s="3"/>
       <c r="E21" s="3"/>
@@ -919,7 +929,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="3:10" x14ac:dyDescent="0.35">
+    <row r="22" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C22" s="4"/>
       <c r="D22" s="4"/>
       <c r="E22" s="4"/>
@@ -932,7 +942,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="3:10" x14ac:dyDescent="0.35">
+    <row r="23" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C23" s="3"/>
       <c r="D23" s="3"/>
       <c r="E23" s="3"/>
@@ -945,7 +955,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="3:10" x14ac:dyDescent="0.35">
+    <row r="24" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C24" s="4"/>
       <c r="D24" s="4"/>
       <c r="E24" s="4"/>
@@ -958,7 +968,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="3:10" x14ac:dyDescent="0.35">
+    <row r="25" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C25" s="3"/>
       <c r="D25" s="3"/>
       <c r="E25" s="3"/>
@@ -971,7 +981,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="3:10" x14ac:dyDescent="0.35">
+    <row r="26" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C26" s="4"/>
       <c r="D26" s="4"/>
       <c r="E26" s="4"/>
@@ -984,7 +994,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="3:10" x14ac:dyDescent="0.35">
+    <row r="27" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C27" s="3"/>
       <c r="D27" s="3"/>
       <c r="E27" s="3"/>
@@ -997,7 +1007,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="3:10" x14ac:dyDescent="0.35">
+    <row r="28" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C28" s="4"/>
       <c r="D28" s="4"/>
       <c r="E28" s="4"/>
@@ -1010,7 +1020,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="3:10" x14ac:dyDescent="0.35">
+    <row r="29" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C29" s="3"/>
       <c r="D29" s="3"/>
       <c r="E29" s="3"/>
@@ -1023,7 +1033,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="3:10" x14ac:dyDescent="0.35">
+    <row r="30" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C30" s="4"/>
       <c r="D30" s="4"/>
       <c r="E30" s="4"/>
@@ -1036,7 +1046,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="3:10" x14ac:dyDescent="0.35">
+    <row r="31" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C31" s="3"/>
       <c r="D31" s="3"/>
       <c r="E31" s="3"/>
@@ -1049,7 +1059,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="3:10" x14ac:dyDescent="0.35">
+    <row r="32" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C32" s="4"/>
       <c r="D32" s="4"/>
       <c r="E32" s="4"/>
@@ -1062,7 +1072,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="3:10" x14ac:dyDescent="0.35">
+    <row r="33" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C33" s="3"/>
       <c r="D33" s="3"/>
       <c r="E33" s="3"/>
@@ -1075,7 +1085,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="3:10" x14ac:dyDescent="0.35">
+    <row r="34" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C34" s="4"/>
       <c r="D34" s="4"/>
       <c r="E34" s="4"/>
@@ -1088,7 +1098,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="3:10" x14ac:dyDescent="0.35">
+    <row r="35" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C35" s="3"/>
       <c r="D35" s="3"/>
       <c r="E35" s="3"/>
@@ -1101,7 +1111,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="3:10" x14ac:dyDescent="0.35">
+    <row r="36" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C36" s="5" t="s">
         <v>6</v>
       </c>
